--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:49</t>
+    <t xml:space="preserve">2026-09-09 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:54</t>
+    <t xml:space="preserve">2026-09-18 10:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1107,12 +1107,12 @@
         <v>28</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>71.11</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1121,12 +1121,12 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>78</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1135,12 +1135,12 @@
         <v>30</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>89.71</v>
+        <v>92.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1149,12 +1149,12 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>38.99</v>
+        <v>71.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1163,12 +1163,12 @@
         <v>29</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>74.2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -1177,7 +1177,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>92.87</v>
+        <v>89.71</v>
       </c>
     </row>
     <row r="8">
@@ -1266,7 +1266,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
@@ -1275,12 +1275,12 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>95.1</v>
+        <v>94.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
@@ -1289,12 +1289,12 @@
         <v>32</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>96.55</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
@@ -1303,12 +1303,12 @@
         <v>31</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>94.79</v>
+        <v>95.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -1317,7 +1317,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>93.8</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="18">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -1387,12 +1387,12 @@
         <v>33</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>89.29</v>
+        <v>90.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>9</v>
@@ -1401,12 +1401,12 @@
         <v>34</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>87.27</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>9</v>
@@ -1415,12 +1415,12 @@
         <v>33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>90.35</v>
+        <v>89.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>9</v>
@@ -1429,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>89.11</v>
+        <v>87.27</v>
       </c>
     </row>
     <row r="26">

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:45</t>
+    <t xml:space="preserve">2026-09-23 16:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:28</t>
+    <t xml:space="preserve">2026-10-05 06:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
